--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0104.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0104.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>EntityCommonTag cơ sở huấn luyện đã tồn tại</t>
+          <t>Thẻ Thực thể Cơ sở Huấn luyện đã tồn tại</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Lỗi loại chức năng thực thể</t>
+          <t>Lỗi loại hàm thực thể</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Không có mục nhập cho việc tạo dungeon được yêu cầu</t>
+          <t>Không tìm thấy lối vào cho bản đồ ngục tạo yêu cầu</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Không có cấu hình mục nhập cho việc tạo dungeon được yêu cầu</t>
+          <t>Không tìm thấy cấu hình vào cho bản đồ ngục tạo yêu cầu</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Mục nhập bị khóa cho việc tạo dungeon được yêu cầu</t>
+          <t>Mục bị khóa cho việc tạo hầm ngục yêu cầu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Phiên bản hiện tại đã hết hạn</t>
+          <t>Phiên bản hiện tại đã hết hạn.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Không đủ số lần thử cho việc tạo dungeon được yêu cầu</t>
+          <t>Không đủ lượt tạo Tổ Tacet theo yêu cầu</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng đủ điều kiện cho việc tạo dungeon được yêu cầu</t>
+          <t>Chưa đủ điều kiện để tạo phó bản yêu cầu</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Cấu hình số lần thử nhập không tồn tại cho dungeon</t>
+          <t>Cấu hình nỗ lực xâm nhập không tồn tại cho hầm ngục này</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Cấu hình mục nhập không tồn tại để mở khóa dungeon</t>
+          <t>Không có cấu hình mục để mở khóa hầm ngục</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Không cần mở khóa mục nhập để mở khóa dungeon</t>
+          <t>Không cần mở khóa lối vào để mở khóa hầm ngục</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Mục nhập đã được mở khóa để mở khóa dungeon</t>
+          <t>Bản ghi đã mở khóa để mở hầm ngục</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng đủ điều kiện mục nhập để mở khóa dungeon</t>
+          <t>Chưa đáp ứng đủ điều kiện để mở khóa hầm ngục</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Cấu hình gameplay được yêu cầu truy cập không tồn tại</t>
+          <t>Không tìm thấy cấu hình trò chơi được yêu cầu.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Yêu cầu truy cập gameplay đã được chấp nhận</t>
+          <t>Đã chấp nhận truy cập cấu hình trò chơi.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Yêu cầu truy cập gameplay không thành công</t>
+          <t>Truy cập cấu hình trò chơi thất bại.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Tạo nhân vật câu chuyện thất bại</t>
+          <t>Không tạo được nhân vật trong cốt truyện</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tạo nhân vật câu chuyện bị trùng lặp</t>
+          <t>Tạo lại nhân vật câu chuyện</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Nhân vật câu chuyện không tồn tại</t>
+          <t>Nhân vật cốt truyện không tồn tại</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Thực thể cơ sở thử nghiệm không tồn tại</t>
+          <t>Thực thể cơ sở kiểm tra không tồn tại</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Cấu hình cơ sở thử nghiệm không tồn tại</t>
+          <t>Cấu hình cơ sở kiểm tra không tồn tại</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng đủ điều kiện để kích hoạt cơ sở thử nghiệm</t>
+          <t>Chưa đủ điều kiện để kích hoạt cơ sở thử nghiệm</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng đủ điều kiện để hủy cơ sở thử nghiệm</t>
+          <t>Chưa đủ điều kiện để hủy cơ sở thử nghiệm</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Mutterfly base đã kích hoạt</t>
+          <t>Trạm Mutterfly đã kích hoạt</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Mutterfly base không tồn tại</t>
+          <t>Trạm Mutterfly không tồn tại</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Thực thể Cast không tồn tại</t>
+          <t>Thực thể kích hoạt không tồn tại</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>ID tính toán Cast không tồn tại</t>
+          <t>ID tính toán kỹ năng không tồn tại</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>ID cấu hình Cast không tồn tại</t>
+          <t>ID cấu hình kỹ năng không tồn tại</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Cấu hình nhân vật hiện tại của Cast không tồn tại</t>
+          <t>Cấu hình nhân vật hiện tại không tồn tại</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>ID Dungeon không tồn tại</t>
+          <t>ID Hầm không tồn tại</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Thực thể Levitation không tồn tại</t>
+          <t>Thực thể bay lơ lửng không tồn tại</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Cấu hình Levitation không tồn tại</t>
+          <t>Cấu hình bay lơ lửng không tồn tại</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Cấu hình nhóm Levitation không tồn tại</t>
+          <t>Cấu hình nhóm bay lơ lửng không tồn tại</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Levitation bị khóa</t>
+          <t>Đã khóa trạng thái bay lơ lửng</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Nhóm Levitation bị khóa</t>
+          <t>Nhóm bay lơ lửng đã bị khóa</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Vật phẩm Levitation không thể đặt tại vị trí này</t>
+          <t>Vật phẩm bay không thể đặt tại vị trí này</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Đã áp dụng Levitation</t>
+          <t>Đã kích hoạt trạng thái bay lơ lửng</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Chưa áp dụng Levitation</t>
+          <t>Không áp dụng trạng thái bay lơ lửng</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Vật phẩm đang được Levitation bởi người chơi khác</t>
+          <t>Vật phẩm đang được người chơi khác nâng lên.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Not Vật tư</t>
+          <t>Không phải vật tư</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Dữ liệu Supply chưa được khởi tạo</t>
+          <t>Dữ liệu tiếp tế chưa được khởi tạo</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Supply chưa được cấu hình</t>
+          <t>Chưa cấu hình vật tư</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Đã nhận Supply</t>
+          <t>Đã nhận vật tư</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Hộp tiếp tế không thể tương tác</t>
+          <t>Hàng tiếp tế không thể tương tác</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>ID hộp tiếp tế không tồn tại</t>
+          <t>ID thả hàng tiếp tế không tồn tại</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Thả hộp tiếp tế thất bại</t>
+          <t>Vật tư không rơi ra được</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Thực thể hộp tiếp tế không tồn tại</t>
+          <t>Đơn vị tiếp tế không tồn tại</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Thẻ Hộp tiếp tế không hợp lệ</t>
+          <t>Thẻ Hỗ trợ không hợp lệ</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Hộp tiếp tế đã có thẻ này</t>
+          <t>Vật tư đã có thẻ này</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Thiếu thẻ Hộp tiếp tế</t>
+          <t>Thiếu thẻ vật tư</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Chế độ ẩn thân đã tắt</t>
+          <t>Tàng hình đã bị vô hiệu hóa</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Đặt lại ẩn thân hoàn tất</t>
+          <t>Đặt lại tàng hình hoàn tất</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Lưu dữ liệu địa hình thất bại</t>
+          <t>Không thể lưu dữ liệu địa hình</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hiện không ở trong dungeon</t>
+          <t>Hiện không ở trong hầm ngục</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Lệnh không hợp lệ, không thể tạo dungeon Solaris</t>
+          <t>Lệnh không hợp lệ, không thể tạo hầm Solaris</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Lệnh không hợp lệ, người chơi đang ở trong dungeon</t>
+          <t>Lệnh không hợp lệ, người chơi đang ở trong hầm</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Tương tác Flow với thực thể quá nhiều</t>
+          <t>Tương tác Dòng Chảy với thực thể quá nhiều lần</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Xác minh thành công, di chuyển theo tọa độ đã bật</t>
+          <t>Xác minh thành công, kích hoạt di chuyển tọa độ.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Xác minh thất bại, di chuyển theo tọa độ bị hạn chế</t>
+          <t>Xác minh thất bại, di chuyển bị hạn chế tọa độ</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Xác minh thất bại, không có dữ liệu tìm đường được xuất cho bản đồ này</t>
+          <t>Xác minh thất bại, không có dữ liệu tìm đường cho bản đồ này</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Không thể thay đổi Solaris khi đang ở trong dungeon</t>
+          <t>Không thể thay đổi Solaris khi đang trong hầm ngục</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Chủ sở hữu không phải Solaris không thể nhận Hộp tiếp tế</t>
+          <t>Người không sở hữu Solaris không thể nhận Hỗ Trợ Vật Tư</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>ID dungeon không tồn tại, vui lòng xác nhận dữ liệu front-end khớp</t>
+          <t>ID Hầm không tồn tại, vui lòng xác nhận dữ liệu giao diện khớp</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Cấu hình thực thể cố định không tồn tại</t>
+          <t>Không tìm thấy cấu hình thực thể cố định</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Không tìm thấy thực thể cố định của cảnh quan</t>
+          <t>Không tìm thấy thực thể cảnh quan cố định</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Không tìm thấy thực thể toàn cầu của địa hình</t>
+          <t>Không tìm thấy thực thể địa hình toàn cục</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Cấu hình thực thể không được đặt là kiểu cố định</t>
+          <t>Cấu hình thực thể chưa được đặt là loại cố định</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Cấu hình thực thể không được đặt là kiểu nhân vật</t>
+          <t>Cấu hình thực thể chưa được đặt là loại nhân vật</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Cấu hình thực thể không được đặt ở chế độ ngủ</t>
+          <t>Cấu hình thực thể chưa được đặt ở chế độ ngủ</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Thực thể không ở trạng thái ngã quỵ</t>
+          <t>Thực thể không ở trạng thái suy yếu</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Ngữ cảnh đánh thức thực thể không hợp lệ</t>
+          <t>Ngữ cảnh thức tỉnh thực thể không hợp lệ</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Thực thể có thuộc tính xung đột</t>
+          <t>Thực thể có xung đột thuộc tính</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Lỗi Guid tùy chọn tương tác</t>
+          <t>Lỗi tùy chọn tương tác Guid</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Lỗi thêm tùy chọn tương tác</t>
+          <t>Lỗi khi thêm tùy chọn tương tác</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Lỗi xóa tùy chọn tương tác</t>
+          <t>Lỗi khi xóa tùy chọn tương tác</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Đặt biến thực thể không hợp lệ</t>
+          <t>Đặt thể hiện biến không hợp lệ</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Lỗi giá trị bên phải khi lấy biến</t>
+          <t>Lỗi giá trị quyền truy cập biến đã đặt</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Lỗi giá trị bên trái khi lấy biến</t>
+          <t>Lỗi thiết lập giá trị biến thu thập bên trái</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Chạy ngữ cảnh biến không hợp lệ</t>
+          <t>Ngữ cảnh biến chạy không hợp lệ</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Chạy thực thể biến không hợp lệ</t>
+          <t>Thể hiện biến chạy không hợp lệ</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Lỗi khi lấy biến không hợp lệ</t>
+          <t>Lỗi thu thập biến không hợp lệ khi chạy</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Danh mục lấy biến không hợp lệ</t>
+          <t>Lỗi phân loại biến thu thập không hợp lệ khi chạy</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Hàm lấy biến không hợp lệ</t>
+          <t>Lỗi hàm thu thập biến không hợp lệ khi chạy</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Lỗi kết quả thiết lập biến</t>
+          <t>Lỗi thiết lập kết quả biến chạy không hợp lệ</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Thực thể Behavior không tồn tại</t>
+          <t>Thực thể hành vi không tồn tại</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Thực thể Behavior không có cấu hình thành phần tương tác</t>
+          <t>Thực thể hành vi không có cấu hình thành phần tương tác</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>ID Behavior không tồn tại</t>
+          <t>ID hành vi không tồn tại</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Bảng điều khiển Behavior không tồn tại</t>
+          <t>Bảng hành vi không tồn tại</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Nút cây Behavior không tồn tại</t>
+          <t>Không tồn tại nút cây hành vi</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Nút tác vụ phụ không chính xác</t>
+          <t>Nút nhiệm vụ phụ không chính xác</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Lỗi chuyển đổi tham số Behavior</t>
+          <t>Lỗi chuyển đổi tham số hành vi</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Ngữ cảnh Behavior không phải là thực thể</t>
+          <t>Ngữ cảnh hành vi không phải là một thực thể</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Không tìm thấy người thực hiện Behavior</t>
+          <t>Không tìm thấy người thực hiện hành vi</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Không tìm thấy hộp thoại Behavior</t>
+          <t>Không tìm thấy lời thoại hành vi</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Tạo ID hộp thoại Behavior thất bại</t>
+          <t>Không tạo được ID hộp thoại hành vi</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Hội tụ đường dẫn Behavior thất bại</t>
+          <t>Không thể hội tụ lộ trình hành vi</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Behavior</t>
+          <t>Không tìm thấy cấu hình hành vi</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Không tìm thấy hàm xử lý Behavior</t>
+          <t>Không tìm thấy hàm xử lý hành vi</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Lỗi Behavior nội bộ</t>
+          <t>Lỗi hành vi nội bộ</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Chỉ mục Behavior bị hạn chế</t>
+          <t>Ghi chú hành vi bị hạn chế</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Không phải là subscript hành vi phía máy chủ</t>
+          <t>Không phải hành vi đăng ký phía máy chủ</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Hành vi phía máy chủ còn lại chưa hoàn thành</t>
+          <t>Hành vi phía máy chủ chưa hoàn tất</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Người thực hiện không phải là cây hành vi</t>
+          <t>Một kẻ không theo khuôn mẫu hành vi</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Hành vi hiện tại không bền vững</t>
+          <t>Hành vi hiện tại không thể duy trì lâu dài</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Thực thể đặt lại vị trí không tồn tại</t>
+          <t>Thực thể vị trí đặt lại không tồn tại</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Thực thể sửa vị trí bất thường không tồn tại</t>
+          <t>Sửa lỗi thực thể vị trí bất thường không tồn tại</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Thực thể yêu cầu loại bỏ đã kiểm tra không tồn tại</t>
+          <t>Yêu cầu xóa thực thể kiểm tra đã được xác nhận không tồn tại</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Thực thể chết đuối không tồn tại</t>
+          <t>Thực thể chìm không tồn tại</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Câu đố va chạm không tồn tại</t>
+          <t>Không tồn tại câu đố va chạm</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Thực thể thoát chiến đấu không tồn tại</t>
+          <t>Không thể thoát chiến đấu: Đối tượng không tồn tại</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Yêu cầu điều chỉnh hệ số độ dai bổ sung không tồn tại</t>
+          <t>Yêu cầu điều chỉnh hệ số cứng cáp bổ sung không tồn tại</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Đối tượng hấp thụ không tồn tại</t>
+          <t>Đối tượng hấp phụ không tồn tại</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Điều kiện hấp thụ không được đáp ứng</t>
+          <t>Điều kiện hấp phụ không đạt</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Bộ chọn thời gian không khả dụng trong chế độ hợp tác</t>
+          <t>Không thể chọn thời gian trong chế độ hợp tác</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Bộ chọn thời gian: Thiếu thành phần bộ chọn thực thể</t>
+          <t>Bộ chọn thời gian: Thiếu thành phần chọn thực thể</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Bộ chọn thời gian: Thành phần bộ chọn không chính xác</t>
+          <t>Bộ chọn thời gian: Thành phần chọn không chính xác</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Bộ chọn thời gian: Thành phần bộ chọn đã hoàn thành</t>
+          <t>Bộ chọn thời gian: Thành phần chọn đã hoàn thành</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Bộ chọn thời gian: Lỗi hướng bộ chọn</t>
+          <t>Bộ chọn thời gian: Lỗi hướng chọn</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Bộ chọn thời gian: Thành phần bộ chọn không ở chế độ bộ chọn</t>
+          <t>Bộ chọn thời gian: Thành phần chọn không ở chế độ chọn</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Invalid Token</t>
+          <t>Mã thông báo không hợp lệ</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Hành động bị hạn chế phía máy khách</t>
+          <t>Hành động máy khách bị hạn chế</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Hành động bị hạn chế phía máy khách</t>
+          <t>Hành động máy khách bị hạn chế</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Lỗi hệ thống</t>
+          <t>Lỗi Hệ Thống</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Hành động bị hạn chế</t>
+          <t>Hành động máy khách bị hạn chế</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Invalid Message Request</t>
+          <t>Yêu cầu tin nhắn không hợp lệ</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Lỗi nhân vật thân mật</t>
+          <t>Lỗi nhân vật thân tình</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Lỗi cấu hình thân mật</t>
+          <t>Lỗi cấu hình thân tình</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Lỗi nhiệm vụ thân mật</t>
+          <t>Lỗi nhiệm vụ thân tình</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Lỗi phần thưởng cấp độ thân mật</t>
+          <t>Lỗi phần thưởng cấp độ thân tình</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Lỗi chấp nhận nhiệm vụ thân mật</t>
+          <t>Lỗi nhận nhiệm vụ thân tình</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Phân đoạn hiện tại của Intimacy bị khóa</t>
+          <t>Mục Gắn Kết hiện tại bị khóa</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Thang máy bị khóa</t>
+          <t>Thang máy đã bị khóa</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Thang máy không di chuyển tiến</t>
+          <t>Thang máy không di chuyển</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Thang máy không ở vị trí ban đầu</t>
+          <t>Thang máy chưa rời vị trí ban đầu</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Thang máy không ở vị trí cuối</t>
+          <t>Thang máy chưa đến vị trí cuối</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Cấp độ thang máy bị hạn chế</t>
+          <t>Tầng thang máy bị hạn chế</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Không tìm thấy người chơi hoặc người chơi offline</t>
+          <t>Không tìm thấy Vận Mệnh Giả hoặc Vận Mệnh Giả đang ngoại tuyến</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Chủ nhân Solaris đã bật chế độ Co-op</t>
+          <t>Chủ nhân Solaris đã bật chế độ hợp tác</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Đã đạt số lượng người chơi Co-op tối đa</t>
+          <t>Đã đạt số lượng người chơi đồng hành tối đa</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Chủ nhân Solaris chỉ cho phép bạn bè tham gia</t>
+          <t>Chủ nhân Solaris chỉ cho phép bạn bè gửi yêu cầu tham gia</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Chủ thế giới đã chặn tất cả yêu cầu Co-op</t>
+          <t>Chủ thế giới đã chặn tất cả yêu cầu Hợp Tác</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Bạn đã bị chặn bởi người chơi này</t>
+          <t>Cậu đã bị chặn bởi người chơi này</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Không thể tham gia thế giới có SOL3 Giai đoạn cao hơn</t>
+          <t>Không thể tham gia thế giới có Giai Đoạn SOL3 cao hơn</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Chủ thế giới đã tắt chế độ Co-op</t>
+          <t>Chủ thế giới đã tắt Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Chủ thế giới hiện đang trong nhiệm vụ chỉ dành cho Chơi đơn</t>
+          <t>Chủ thế giới hiện đang trong nhiệm vụ Chơi Đơn</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Đã ở Chế độ Co-op</t>
+          <t>Đang ở Chế Độ Hợp Tác rồi</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Hiện đang trong nhiệm vụ chỉ dành cho Chơi đơn</t>
+          <t>Đang trong nhiệm vụ chỉ dành cho Chơi Đơn</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Đã tắt Chế độ Co-op</t>
+          <t>Chế độ Đồng Đội đã bị vô hiệu hóa</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Đã gửi yêu cầu tham gia Solaris</t>
+          <t>Đã gửi yêu cầu gia nhập Solaris</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15414,7 +15414,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Không thể tham gia Solaris của chính bạn</t>
+          <t>Không thể tham gia Solaris của chính mình</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Yêu cầu đã hết thời gian chờ</t>
+          <t>Yêu cầu hết thời gian chờ</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Đang vào Solaris của người chơi, vui lòng đợi</t>
+          <t>Đang kết nối người chơi với Solaris, xin chờ</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Đang đợi người chơi tham gia Solaris, vui lòng đợi</t>
+          <t>Đang đợi người chơi tham gia Solaris, xin chờ giây lát</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Hàng đợi tham gia đã đầy, vui lòng đợi</t>
+          <t>Hàng chờ tham gia đã đầy, vui lòng đợi</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Đã trong hàng đợi tham gia</t>
+          <t>Đã vào hàng chờ tham gia rồi</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chủ Solaris không ở trong Solaris</t>
+          <t>Chủ nhân Solaris không ở trong Solaris</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Người chơi không ở trong Solaris</t>
+          <t>Vận Mệnh Giả không ở Solaris-3</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Không ở trong hàng đợi tham gia</t>
+          <t>Không trong hàng chờ tham gia</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Không tìm thấy người chơi</t>
+          <t>Không tìm thấy Vận Mệnh Giả</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Chủ thế giới hiện đang dùng Resonator thử nghiệm, không thể tham gia Co-op</t>
+          <t>Chủ thế giới đang dùng Resonator thử nghiệm, không thể tham gia Hợp Tác</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Chủ thế giới hiện đang dùng Resonator thử nghiệm, không thể tham gia Co-op</t>
+          <t>Chủ thế giới đang dùng Resonator thử nghiệm, không thể tham gia Hợp Tác</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Gửi yêu cầu thất bại, người chơi hiện đang tìm trận Co-op</t>
+          <t>Gửi yêu cầu thất bại, người chơi đang trong quá trình ghép cặp co-op</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Không thể chấp nhận yêu cầu trong khi đang tìm trận Co-op</t>
+          <t>Không thể chấp nhận yêu cầu trong lúc ghép đội hợp tác</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Invalid GM</t>
+          <t>GM không hợp lệ</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Sự kiện chưa bắt đầu</t>
+          <t>Sự kiện chưa bắt đầu.</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Mã đổi đã được sử dụng</t>
+          <t>Mã đổi quà đã được sử dụng</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Mã đổi đã được sử dụng</t>
+          <t>Mã đổi quà đã được sử dụng</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Mã đổi hiện không đáp ứng điều kiện đổi</t>
+          <t>Mã đổi quà hiện không đáp ứng điều kiện đổi</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Mã đổi đã hết hạn</t>
+          <t>Mã đổi quà đã hết hạn rồi.</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Chức năng CdKey chưa được kích hoạt</t>
+          <t>Chức năng Nhập CdKey chưa được kích hoạt</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Mã đổi chưa có hiệu lực</t>
+          <t>Mã đổi quà vẫn chưa có hiệu lực.</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Số lần đổi hiện tại quá nhiều, vui lòng thử lại sau</t>
+          <t>Số lần đổi quà hiện tại quá nhiều, hãy thử lại sau</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Số lần đổi hiện tại quá nhiều, vui lòng thử lại sau</t>
+          <t>Số lần đổi quà hiện tại quá nhiều, hãy thử lại sau</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Không thể mô phỏng thời tiết tại thời điểm hiện tại</t>
+          <t>Không thể mô phỏng thời tiết vào thời điểm hiện tại</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Không thể mô phỏng thời tiết tại khu vực hiện tại</t>
+          <t>Không thể mô phỏng thời tiết ở khu vực hiện tại</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Không thể mô phỏng thời tiết tại khu vực hiện tại</t>
+          <t>Không thể mô phỏng thời tiết ở khu vực hiện tại</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Không thể mô phỏng thời tiết khi đang chiến đấu</t>
+          <t>Bạn không thể mô phỏng thời tiết khi đang chiến đấu</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Không thể mô phỏng thời tiết trong chế độ Co-op</t>
+          <t>Bạn không thể mô phỏng thời tiết trong chế độ Đồng Đội</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Sky Projection Array Control Mô-đun Locked</t>
+          <t>Mô-đun Điều Khiển Mảng Chiếu Hình Trên Không Đã Bị Khóa</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Sky Projection Array Control Mô-đun Locked</t>
+          <t>Mô-đun Điều Khiển Mảng Chiếu Hình Trên Không Đã Bị Khóa</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Chương X - Hồi X $[begin]</t>
+          <t>Chương X - Hồi X $[Bắt đầu]</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Chương X - Hồi X $[End]</t>
+          <t>Chương X - Hồi X $[Kết thúc]</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Phụ</t>
+          <t>Nhiệm Vụ Phụ</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hoàn thành</t>
+          <t>Nhiệm Vụ Hoàn Thành</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Phần Thưởng Bị Khóa Thời Gian</t>
+          <t>Phần thưởng bị khóa theo thời gian</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Claimed</t>
+          <t>Đã nhận</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Combat Event</t>
+          <t>Sự Kiện Chiến Đấu</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Leisure Event</t>
+          <t>Sự Kiện Nhàn Hạ</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Exploration Event</t>
+          <t>Sự Kiện Thám Hiểm</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Failed</t>
+          <t>Thất bại</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Calculation Error</t>
+          <t>Lỗi Tính Toán</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Choice Supply Pack</t>
+          <t>Gói Vật Tư Lựa Chọn</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Tower of Adversity F1</t>
+          <t>Tháp Nghịch Cảnh Tầng 1</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Tower of Adversity F2</t>
+          <t>Tháp Thử Thách Tầng 2</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Tower of Adversity F3</t>
+          <t>Tháp Thử Thách Tầng 3</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tower of Adversity F4</t>
+          <t>Tháp Thử Thách Tầng 4</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Tower of Adversity F5</t>
+          <t>Tháp Thử Thách Tầng 5</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Tower of Adversity F6</t>
+          <t>Tháp Thử Thách Tầng 6</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Tower of Adversity F7</t>
+          <t>Tháp Thử Thách Tầng 7</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Tower of Adversity F8</t>
+          <t>Tháp Thử Thách Tầng 8</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Tower of Adversity F9</t>
+          <t>Tháp Thử Thách Tầng 9</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Tương tác với Sound String để kích hoạt Sonoro Sphere</t>
+          <t>Tương tác với Dây Âm Thanh để kích hoạt Sonoro Sphere</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Sound Wave</t>
+          <t>Sóng Âm</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Sound Wave</t>
+          <t>Sóng Âm</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Sound Wave</t>
+          <t>Sóng Âm</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Sound Wave</t>
+          <t>Sóng Âm</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Mở khóa Tacet Field</t>
+          <t>Tổ Tacet đã mở khóa</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Mở khóa Tacet Field</t>
+          <t>Tổ Tacet đã mở khóa</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Tìm Camellya</t>
+          <t>Tìm Camellya đi</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Phụ</t>
+          <t>Nhiệm Vụ Phụ</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hoàn thành</t>
+          <t>Nhiệm Vụ Hoàn Thành</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Countdown</t>
+          <t>Đếm Ngược</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Current Progress: 0/100</t>
+          <t>Tiến độ hiện tại: 0/100</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả hướng dẫn để hoàn thành Thử Thách</t>
+          <t>Hoàn thành tất cả hướng dẫn để vượt qua Thử Thách</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Nhân vật Thử nghiệm</t>
+          <t>Nhân vật thử nghiệm</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>New Entry Unlocked</t>
+          <t>Mục Mới Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Healing Complete</t>
+          <t>Hoàn tất hồi phục</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Cần Chìa Khóa Kim Loại để mở</t>
+          <t>Yêu cầu Chìa Khóa Kim Loại để mở</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Hoàn tất</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách lần đầu</t>
+          <t>Hoàn Thành Thử Thách Lần Đầu</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Đứng lên để đặt Ghi Chú</t>
+          <t>Đứng lên để đặt Memo</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Người chơi này đã có trong danh sách Lời Mời Kết Bạn của bạn</t>
+          <t>Người chơi này đã có trong danh sách Lời Mời Kết Bạn của cậu rồi</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Người chơi này đã là Bạn bè của bạn</t>
+          <t>Người chơi này đã là bạn của cậu rồi</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Bạn đã gửi yêu cầu trước đó</t>
+          <t>Bạn đã gửi đơn đăng ký trước đó rồi.</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Bạn đã đạt giới hạn số lần gửi yêu cầu hàng ngày</t>
+          <t>Bạn đã đạt giới hạn số lần nộp đơn hàng ngày.</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Pioneer Podcast Not Available</t>
+          <t>Podcast Tiên Phong không khả dụng</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Pioneer Podcast Vật phẩm Not Available</t>
+          <t>Vật phẩm Podcast Tiên Phong không khả dụng</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Chặng phụ bị khóa</t>
+          <t>Né Tránh Bên Bị Khóa</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Mục này không khả dụng để tùy chỉnh</t>
+          <t>Tính năng này không khả dụng để tùy chỉnh.</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Không thể đặt Ghi Chú trong Chế Độ Hợp Tác</t>
+          <t>Không thể đặt Ghi Chú trong Chế độ Hợp Tác</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Bạn không thể đặt Ghi Chú lúc này</t>
+          <t>Bạn không thể đặt Ghi Chú lúc này.</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Hằng ngày</t>
+          <t>Nhiệm Vụ Hằng Ngày Hoàn Thành</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Không thể mở bản đồ</t>
+          <t>Không thể mở Bản đồ</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Tạm thời không thể Neo Đậu</t>
+          <t>Chức năng Móc tạm thời bị vô hiệu hóa</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Hoverdroid: Shooter không thể sử dụng trong cảnh hiện tại</t>
+          <t>Robot Bay Lượn: Bộ phận bắn không thể sử dụng trong cảnh hiện tại</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23954,7 +23954,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Friend Request Sent</t>
+          <t>Đã Gửi Yêu Cầu Kết Bạn</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Bạn đã bị xóa khỏi danh sách bạn bè của người chơi hiện tại</t>
+          <t>Bạn đã bị người chơi hiện tại xóa kết bạn.</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Danh sách bạn bè đã đầy</t>
+          <t>Danh sách bạn bè của bạn đã đầy</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Tối đa 12 ký tự</t>
+          <t>12 ký tự tối đa</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Friend Request Expired</t>
+          <t>Yêu Cầu Kết Bạn Đã Hết Hạn</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Kết quả sẽ có hiệu lực vào ngày tiếp theo</t>
+          <t>Kết quả sẽ có hiệu lực vào ngày hôm sau</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Disliked</t>
+          <t>Không ưa thích</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Liked</t>
+          <t>Đã thích</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Đã đặt Ghi chú tại đây</t>
+          <t>Đã đặt Ghi Chú tại đây</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Thao tác quá thường xuyên</t>
+          <t>Thao tác quá nhanh</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Người chơi này đã có trong Danh sách chặn của bạn</t>
+          <t>Người chơi này đã có trong Danh sách Chặn của bạn</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Người chơi này không có trong Danh sách chặn của bạn</t>
+          <t>Người chơi này không có trong Danh Sách Chặn của cậu</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Insufficient Credits</t>
+          <t>Credits không đủ</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Log Upload Canceled</t>
+          <t>Hủy tải nhật ký lên</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Vui lòng thực hiện thao tác sau khi nhật ký được nén</t>
+          <t>Vui lòng thực hiện hành động sau khi nhật ký được nén</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Đánh dấu "xác nhận" trước khi tải lên</t>
+          <t>Bấm "xác nhận" trước khi tải lên</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Đã nhận tất cả tệp đính kèm Thư</t>
+          <t>Đã nhận toàn bộ tệp đính kèm trong Thư</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Thư đã bị xóa</t>
+          <t>Thư đã xóa</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Thư đã được thu hồi</t>
+          <t>Thư đã thu hồi</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Đã nhận phần thưởng</t>
+          <t>Đã Nhận Phần Thưởng</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Tên trống</t>
+          <t>Tên Hư Không</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Bạn cần đặt ít nhất một nhân vật trong đội</t>
+          <t>Cậu cần đặt ít nhất một nhân vật vào đội hình.</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Bạn hiện không thể sử dụng chức năng này</t>
+          <t>Hiện tại bạn không thể sử dụng chức năng này.</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Không có khóa để đặt lại</t>
+          <t>Không thể đặt lại phím</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Người chơi này không có trong Danh sách bạn bè của bạn</t>
+          <t>Người chơi này không có trong Danh sách Bạn bè của bạn</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Danh sách bạn bè của người chơi này đã đầy</t>
+          <t>Danh sách Bạn Bè của người chơi này đã đầy</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Không thể vào hướng dẫn khi đang ở chế độ hợp tác</t>
+          <t>Không thể vào hướng dẫn khi đang ở Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mở khóa</t>
+          <t>Chưa đáp ứng yêu cầu mở khóa</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Đã lưu thay đổi phím</t>
+          <t>Đã lưu Thay Đổi Chính</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Saved</t>
+          <t>Đã Lưu</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Vui lòng cho nguyên liệu vào</t>
+          <t>Vui lòng đặt nguyên liệu vào</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Resonator thử nghiệm đã vào đội</t>
+          <t>Resonator Thử Nghiệm đã tham gia đội</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Resonator thử nghiệm đã rời đội</t>
+          <t>Resonator Thử Nghiệm đã rời đội</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Không thể điều chỉnh đội hình khi đang trong Resonator Trial</t>
+          <t>Không thể thay đổi đội hình khi đang trong Thử Thách Resonator</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Không thể Dịch Chuyển Nhanh với Nhân Vật Thử Nghiệm</t>
+          <t>Nhân vật thử nghiệm không thể Dịch Chuyển Tức Thời</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Đã đổi phiếu đăng ký</t>
+          <t>Đã đổi phiếu đăng ký thành công</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Absorb</t>
+          <t>Hấp Thu</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Ingredient</t>
+          <t>Nguyên liệu</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Vật phẩm Obtained</t>
+          <t>Đã nhận được vật phẩm</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Số lần mở</t>
+          <t>Số lượng lỗ hổng</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Hành động</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Điểm cao nhất</t>
+          <t>Điểm Số Cao Nhất</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Best Time</t>
+          <t>Thời Gian Tốt Nhất</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Không Record</t>
+          <t>Không có bản ghi</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Collected</t>
+          <t>Đã thu thập</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Có Sẵn</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Add</t>
+          <t>Thêm</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Adventure</t>
+          <t>Phiêu lưu</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Sentence #1</t>
+          <t>Câu lệnh số 1</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chọn Từ</t>
+          <t>Chọn Từ Ngữ</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Add Emotes</t>
+          <t>Thêm Biểu Cảm</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Change Sentence</t>
+          <t>Thay Đổi Câu</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Thêm một Câu</t>
+          <t>Thêm Một Câu</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Hoàn thành Memo trống trước</t>
+          <t>Hoàn thành Memo trống trước đã</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Chọn Liên Từ</t>
+          <t>Chọn Liên Kết</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Sentence #2</t>
+          <t>Câu lệnh số 2</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Chọn Từ</t>
+          <t>Chọn Từ Ngữ</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Quá gần với Memo khác</t>
+          <t>Quá gần các Memo khác</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Memo Limit Reached</t>
+          <t>Giới hạn bản ghi nhớ đã đạt đến</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Age-rating Thông báo</t>
+          <t>Thông Báo Xếp Hạng Tuổi</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Mailbox</t>
+          <t>Hộp thư</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Rơi Vật Liệu</t>
+          <t>Rơi Vật Phẩm</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Tham gia Hợp tác</t>
+          <t>Tham Gia Hợp Tác</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Send Friend Request</t>
+          <t>Gửi Lời Mời Kết Bạn</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Rủi ro cao</t>
+          <t>Rủi Ro Cao</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30534,7 +30534,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Medium Risk</t>
+          <t>Mức Rủi Ro Trung Bình</t>
         </is>
       </c>
       <c r="N430" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Phe này sẽ được mở khóa trong các bản khám phá tương lai</t>
+          <t>Phe phái này sẽ được mở khóa trong các chuyến thám hiểm tương lai</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Quay về Tháp</t>
+          <t>Quay lại Tháp</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Chạm vào bất kỳ đâu để đóng</t>
+          <t>Nhấn bất kỳ đâu để đóng</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Hỗ trợ bộ điều khiển sẽ có trong các bản cập nhật tương lai</t>
+          <t>Hỗ trợ bộ điều khiển sẽ có trong các bản cập nhật sau.</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Seasonal Specials</t>
+          <t>Đặc Sản Theo Mùa</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Mở khóa Kênh Connoisseur</t>
+          <t>Mở Kênh Nghệ Nhân</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Xem Kênh Insider</t>
+          <t>Xem Kênh Nội Bộ</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Nâng cấp lên Kênh Connoisseur</t>
+          <t>Nâng cấp lên Kênh Nghệ Nhân</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Xem Kênh Insider</t>
+          <t>Xem Kênh Nội Bộ</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Morning Broadcasts</t>
+          <t>Chương Trình Phát Sóng Buổi Sáng</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn EXP hàng tuần</t>
+          <t>Đã đạt giới hạn Kinh Nghiệm Hàng Tuần</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Star Rebound</t>
+          <t>Phản Xạ Sao</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Đã mở khóa để nhận các phần thưởng sau</t>
+          <t>Mở khóa để nhận những phần thưởng sau</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Nâng cấp lên Kênh Connoisseur để nhận các phần thưởng sau</t>
+          <t>Nâng cấp lên Kênh Nghệ Nhân để nhận những phần thưởng sau</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Insider Channel Unlocked</t>
+          <t>Đã Mở Khóa Kênh Nội Bộ</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Connoisseur Channel Unlocked</t>
+          <t>Đã mở khóa Kênh Nhà sưu tầm</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32354,7 +32354,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Connoisseur Channel Unlocked</t>
+          <t>Đã mở khóa Kênh Nhà sưu tầm</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Weekly Highlights</t>
+          <t>Điểm Nổi Bật Hàng Tuần</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Không thể thay thế nhân vật chưa sở hữu</t>
+          <t>Không thể thay thế Cộng Hưởng Giả chưa sở hữu</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Không thể thay thế nhân vật đã sẵn sàng</t>
+          <t>Không thể thay thế Cộng Hưởng Giả đang sẵn sàng</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Rover (Nam)</t>
+          <t>Vận Mệnh Giả (Nam)</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Người Bảo Vệ Giọng Hát</t>
+          <t>Người Bảo Vệ Âm Thanh</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Thách Đấu Lại</t>
+          <t>Thử Thách Lại</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Xác Nhận Điểm Số</t>
+          <t>Xác nhận Điểm số</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Xác Nhận</t>
+          <t>Xác nhận</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Common Class</t>
+          <t>Hạng Thường</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Calamity Class</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Nâng Cấp Hoàn Tất</t>
+          <t>Nâng cấp hoàn tất</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>2-Star Echo</t>
+          <t>Âm Hưởng 2 Sao</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>3-Star Echo</t>
+          <t>Hồi Âm 3 Sao</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>4-Star Echo</t>
+          <t>Hồi Âm 4 Sao</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>5-Star Echo</t>
+          <t>Echo 5 Sao</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Insufficient EXP</t>
+          <t>Kinh nghiệm không đủ.</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34104,7 +34104,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Đã đạt cấp độ tối đa</t>
+          <t>Đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Nguồn Cội</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Khôi Phục Dữ Liệu</t>
+          <t>Khôi phục Dữ liệu</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Nâng Cấp Chưa Hoàn Tất</t>
+          <t>Nâng cấp chưa hoàn tất</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Không Đủ Vật Liệu Nâng Cấp</t>
+          <t>Vật liệu nâng cấp không đủ.</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Nút này hiện không khả dụng</t>
+          <t>Nút này hiện không khả dụng.</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Không thể bắt đầu thách đấu trận đấu ở trạng thái hiện tại</t>
+          <t>Không thể khởi động thử thách trận đấu ở trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Không thể thay đổi ngoại hình của Rover trong trận đấu</t>
+          <t>Không thể thay đổi ngoại hình của Rover trong trận chiến</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Không thể thay đổi ngoại hình của Rover trong dungeon</t>
+          <t>Không thể thay đổi ngoại hình của Rover trong hầm ngục</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Bạn không thể sử dụng vật phẩm này</t>
+          <t>Bạn không thể sử dụng vật phẩm này.</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Unmute</t>
+          <t>Bỏ tắt tiếng</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Không thể đổi nhân vật trước khi thách đấu bắt đầu</t>
+          <t>Không thể đổi nhân vật trước khi thử thách bắt đầu</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Không thể đề xuất ở trạng thái này</t>
+          <t>Không thể đề xuất trong trạng thái này</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Hiện không thể tham gia Co-op</t>
+          <t>Hiện không thể tham gia Chế độ Hợp Tác</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Restart</t>
+          <t>Bắt đầu lại</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
